--- a/artfynd/S 780-2025 artfynd.xlsx
+++ b/artfynd/S 780-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AZ116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785585</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785588</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785590</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785613</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1168,6 +1193,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109447677</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109820379</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785578</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785579</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785593</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1677,6 +1727,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126784660</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1774,6 +1829,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785544</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1871,6 +1931,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785587</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785597</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2065,6 +2135,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785627</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2162,6 +2237,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785596</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2259,6 +2339,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785607</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2356,6 +2441,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785591</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2453,6 +2543,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785592</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2550,6 +2645,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785595</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2647,6 +2747,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785598</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2744,6 +2849,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785608</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2841,6 +2951,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785609</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2938,6 +3053,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785618</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3035,6 +3155,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785628</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3144,6 +3269,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88080375</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3241,6 +3371,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785551</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3338,6 +3473,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785589</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3435,6 +3575,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785594</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3543,6 +3688,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109447757</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3640,6 +3790,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785572</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3737,6 +3892,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785552</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3834,6 +3994,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785558</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3931,6 +4096,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785576</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4028,6 +4198,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785584</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4125,6 +4300,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785586</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4222,6 +4402,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785610</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4319,6 +4504,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785631</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4428,6 +4618,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88080447</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4539,6 +4734,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88280465</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4650,6 +4850,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88280466</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4761,6 +4966,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88280469</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4872,6 +5082,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88280470</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4983,6 +5198,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838390</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5091,6 +5311,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109447957</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5188,6 +5413,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785567</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5285,6 +5515,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785568</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5382,6 +5617,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785605</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5479,6 +5719,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785629</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5576,6 +5821,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785633</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5673,6 +5923,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129537358</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5770,6 +6025,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785545</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5867,6 +6127,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785546</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5964,6 +6229,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785555</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6061,6 +6331,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785561</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6158,6 +6433,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785573</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6255,6 +6535,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785577</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6352,6 +6637,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785581</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6449,6 +6739,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785599</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6546,6 +6841,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785601</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6643,6 +6943,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785616</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6740,6 +7045,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785620</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6851,6 +7161,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838250</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6948,6 +7263,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129538361</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7045,6 +7365,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785564</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7142,6 +7467,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785565</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7239,6 +7569,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785543</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7336,6 +7671,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785547</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7433,6 +7773,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785562</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7530,6 +7875,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785580</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7627,6 +7977,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785582</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7724,6 +8079,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785602</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7821,6 +8181,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785617</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7918,6 +8283,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785621</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8030,6 +8400,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126777318</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8127,6 +8502,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785548</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8224,6 +8604,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785549</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8321,6 +8706,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785550</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8418,6 +8808,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785556</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8515,6 +8910,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785566</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8612,6 +9012,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785569</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8709,6 +9114,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785600</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8820,6 +9230,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838248</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8917,6 +9332,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785553</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9014,6 +9434,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785554</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9111,6 +9536,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785559</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9208,6 +9638,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785574</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9322,6 +9757,11 @@
       <c r="AY88" t="inlineStr">
         <is>
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838253</t>
         </is>
       </c>
     </row>
@@ -9425,6 +9865,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126797602</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9526,6 +9971,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126797610</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9627,6 +10077,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126797622</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9728,6 +10183,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126797624</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9825,6 +10285,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785570</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9922,6 +10387,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785604</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10019,6 +10489,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785606</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10135,6 +10610,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838584</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10251,6 +10731,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838088</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10370,6 +10855,11 @@
       <c r="AY98" t="inlineStr">
         <is>
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93973049</t>
         </is>
       </c>
     </row>
@@ -10496,6 +10986,11 @@
       <c r="AY99" t="inlineStr">
         <is>
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93973051</t>
         </is>
       </c>
     </row>
@@ -10606,6 +11101,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129537648</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10714,6 +11214,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129537712</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10822,6 +11327,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129537740</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10919,6 +11429,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785542</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11016,6 +11531,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785560</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11113,6 +11633,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785575</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11210,6 +11735,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785603</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11307,6 +11837,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785611</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11404,6 +11939,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785615</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11501,6 +12041,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785619</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11598,6 +12143,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56785630</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11714,6 +12264,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88280184</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11830,6 +12385,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838089</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11951,6 +12511,11 @@
           <t>Insekter på tallved i Dalarna 2020 - 2021</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96838090</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12063,6 +12628,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126777316</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12169,6 +12739,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109819728</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12281,8 +12856,130 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126777313</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>